--- a/stories/arbres/ATOM-FAM.AID.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est dans la cuisine. Il veut de la confiture. Le pot est fermé. Jules tourne un peu. C'est trop difficile. Jules va vers la porte. Il va vers maman. Maman est près de l'évier. Jules dit : maman. J'ai besoin du pot. Il dit le besoin. Maman écoute. Maman ouvre le pot. Papa arrive. Jules dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Jules tartine le pain. Ça sent la fraise. Papa s'assoit près de lui.</t>
+          <t>Jules est dans la cuisine. Il veut de la confiture. Le pot est fermé. Jules tourne un peu. C'est trop difficile. Jules va vers la porte. Il va vers maman. Maman est près de l'évier. Maman. J'ai besoin du pot. Il dit le besoin. Maman écoute. Maman ouvre le pot. Papa arrive. Jules dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Jules tartine le pain. Ça sent la fraise. Papa s'assoit près de lui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est dans la cuisine. Il veut de la confiture. Le pot est fermé. Jules tourne un peu. C'est trop difficile. Jules va vers la porte. Il va vers maman. Maman est près de l'évier.
+enfant-m|Maman. J'ai besoin du pot. Il dit le besoin. Maman écoute. Maman ouvre le pot. Papa arrive.
+narrateur|Jules dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Jules tartine le pain. Ça sent la fraise. Papa s'assoit près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jules n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a appelé. Il a dit le besoin. Maman a entendu. Le pot est ouvert.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1820,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Jules croque le pain. Papa s'assoit près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1987,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2027,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Jules dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Jules tartine le pain. Ça sent la fraise. Papa s'assoit près de lui.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Jules n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1662,6 +1673,7 @@
           <t>narrateur|Jules a appelé. Il a dit le besoin. Maman a entendu. Le pot est ouvert.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1837,7 @@
           <t>narrateur|Jules croque le pain. Papa s'assoit près de lui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1992,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2010,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2034,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2235,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.AID.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jules appelle maman</t>
+          <t>La cuillère de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une cuillère dort dans la confiture. Nino veut tartiner le pain tiède. Le pot est collé. Il va vers maman et dit le besoin. Le couvercle s'ouvre. Ça sent la fraise.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est dans la cuisine. Il veut de la confiture. Le pot est fermé. Jules tourne un peu. C'est trop difficile. Jules va vers la porte. Il va vers maman. Maman est près de l'évier. Maman. J'ai besoin du pot. Il dit le besoin. Maman écoute. Maman ouvre le pot. Papa arrive. Jules dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Jules tartine le pain. Ça sent la fraise. Papa s'assoit près de lui.</t>
+          <t>La cuillère en bois dort dans une tache de confiture. La tache est rouge et un peu collante. Le rideau jaune ne bouge presque pas. Une mouche tapote la vitre, tout doucement. La cuisine sent le pain encore chaud. Des miettes dorées brillent sur la table. Maman essuie l'évier avec un linge bleu. Papa range les tasses dans le placard. Le pain est encore tiède, Nino. Tu veux un peu de confiture ? En ce moment, Nino pose les mains sur la table. Le bois est lisse, un peu collant aussi. Le pot de confiture est rouge. L'étiquette montre une fraise. Je veux de la confiture, maman. Prends le pot, tout doucement. Nino prend le pot. Le verre est froid et lisse. Il tourne un peu le couvercle. Le couvercle ne vient pas. C'est trop difficile. Il est collé. Nino pose le pot. Il va vers maman. Aller vers eux, c'est possible. Il dit le besoin. Maman. J'ai besoin du pot. Le couvercle est trop dur. Je t'écoute, Nino. Viens. On le tient ensemble. Maman tient le pot. Nino tient le couvercle. Le couvercle fait un petit clic. Le pot s'ouvre. Ça sent la fraise. Bravo. Tu as dit le besoin. Tu es venu vers maman. C'est du bon travail. Merci, maman. Papa s'assoit près de lui. Tu tartines le pain ? Oui, papa. Nino tartine le pain. La confiture est rouge et brillante. Une petite graine de fraise reste sur le couteau. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Le rideau jaune bouge un tout petit peu. La mouche s'en va. Ça sent bon, hein ? Ça sent la fraise. Tu as fini de tartiner ? Presque, maman. Nino goûte un peu de confiture. Le pain est tiède sous ses doigts. Bravo, Nino. La cuillère en bois n'est plus seule.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules est dans la cuisine. Il veut de la confiture. Le pot est fermé. Jules tourne un peu. C'est trop difficile. Jules va vers la porte. Il va vers maman. Maman est près de l'évier.
-enfant-m|Maman. J'ai besoin du pot. Il dit le besoin. Maman écoute. Maman ouvre le pot. Papa arrive.
-narrateur|Jules dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Jules tartine le pain. Ça sent la fraise. Papa s'assoit près de lui.</t>
+          <t>narrateur|La cuillère en bois dort dans une tache de confiture.
+narrateur|La tache est rouge et un peu collante.
+narrateur|Le rideau jaune ne bouge presque pas.
+narrateur|Une mouche tapote la vitre, tout doucement.
+narrateur|La cuisine sent le pain encore chaud.
+narrateur|Des miettes dorées brillent sur la table.
+narrateur|Maman essuie l'évier avec un linge bleu.
+narrateur|Papa range les tasses dans le placard.
+maman|Le pain est encore tiède, Nino.
+papa|Tu veux un peu de confiture ?
+narrateur|En ce moment, Nino pose les mains sur la table.
+narrateur|Le bois est lisse, un peu collant aussi.
+narrateur|Le pot de confiture est rouge.
+narrateur|L'étiquette montre une fraise.
+enfant-m|Je veux de la confiture, maman.
+maman|Prends le pot, tout doucement.
+narrateur|Nino prend le pot.
+narrateur|Le verre est froid et lisse.
+narrateur|Il tourne un peu le couvercle.
+narrateur|Le couvercle ne vient pas.
+narrateur|C'est trop difficile.
+enfant-m|Il est collé.
+narrateur|Nino pose le pot.
+narrateur|Il va vers maman.
+narrateur|Aller vers eux, c'est possible.
+narrateur|Il dit le besoin.
+enfant-m|Maman. J'ai besoin du pot.
+enfant-m|Le couvercle est trop dur.
+maman|Je t'écoute, Nino.
+maman|Viens. On le tient ensemble.
+narrateur|Maman tient le pot.
+narrateur|Nino tient le couvercle.
+narrateur|Le couvercle fait un petit clic.
+narrateur|Le pot s'ouvre.
+narrateur|Ça sent la fraise.
+maman|Bravo. Tu as dit le besoin.
+papa|Tu es venu vers maman.
+papa|C'est du bon travail.
+enfant-m|Merci, maman.
+narrateur|Papa s'assoit près de lui.
+papa|Tu tartines le pain ?
+enfant-m|Oui, papa.
+narrateur|Nino tartine le pain.
+narrateur|La confiture est rouge et brillante.
+narrateur|Une petite graine de fraise reste sur le couteau.
+maman|On peut aller vers eux.
+papa|On peut dire le besoin.
+maman|On peut appeler papa ou maman.
+narrateur|Parce qu'il a dit le besoin, le pot s'ouvre.
+narrateur|Le rideau jaune bouge un tout petit peu.
+narrateur|La mouche s'en va.
+papa|Ça sent bon, hein ?
+enfant-m|Ça sent la fraise.
+maman|Tu as fini de tartiner ?
+enfant-m|Presque, maman.
+narrateur|Nino goûte un peu de confiture.
+narrateur|Le pain est tiède sous ses doigts.
+papa|Bravo, Nino.
+narrateur|La cuillère en bois n'est plus seule.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jules n'arrive pas. Que fait-il ?</t>
+          <t>Nino n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1570,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jules n'arrive pas. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino n'arrive pas.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a appelé. Il a dit le besoin. Maman a entendu. Le pot est ouvert.</t>
+          <t>Nino a appelé. Il est allé vers maman. Il a dit le besoin. Maman a entendu. Le pot est ouvert. Tu es venu me le dire. Bravo. C'est du bon travail, Nino. Tu as fini ta tartine ? Oui, papa. Une miette reste sur la table. Elle brille un peu, comme la confiture.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,10 +1738,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules a appelé. Il a dit le besoin. Maman a entendu. Le pot est ouvert.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a appelé.
+narrateur|Il est allé vers maman.
+narrateur|Il a dit le besoin.
+narrateur|Maman a entendu.
+narrateur|Le pot est ouvert.
+maman|Tu es venu me le dire.
+maman|Bravo.
+papa|C'est du bon travail, Nino.
+papa|Tu as fini ta tartine ?
+enfant-m|Oui, papa.
+narrateur|Une miette reste sur la table.
+narrateur|Elle brille un peu, comme la confiture.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Jules croque le pain. Papa s'assoit près de lui.</t>
+          <t>Nino croque le pain. Ça croustille tout doucement. C'est bon ? C'est bon, papa. Tu veux un verre d'eau ? Oui, maman. Maman pose un verre. L'eau fait un petit bruit clair. Papa s'assoit près de lui. On reste encore un peu ensemble ? Oui. La cuisine est calme. Le rideau jaune est immobile.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,10 +1912,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Jules croque le pain. Papa s'assoit près de lui.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino croque le pain.
+narrateur|Ça croustille tout doucement.
+papa|C'est bon ?
+enfant-m|C'est bon, papa.
+maman|Tu veux un verre d'eau ?
+enfant-m|Oui, maman.
+narrateur|Maman pose un verre.
+narrateur|L'eau fait un petit bruit clair.
+narrateur|Papa s'assoit près de lui.
+papa|On reste encore un peu ensemble ?
+enfant-m|Oui.
+narrateur|La cuisine est calme.
+narrateur|Le rideau jaune est immobile.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Nino. Tu as fait du bon travail. La tache de confiture a disparu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,10 +2091,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai dit le besoin.
+maman|Oui. Tu es venu vers moi.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|La tache de confiture a disparu.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La cuillère en bois dort dans une tache de confiture. La tache est rouge et un peu collante. Le rideau jaune ne bouge presque pas. Une mouche tapote la vitre, tout doucement. La cuisine sent le pain encore chaud. Des miettes dorées brillent sur la table. Maman essuie l'évier avec un linge bleu. Papa range les tasses dans le placard. Le pain est encore tiède, Nino. Tu veux un peu de confiture ? En ce moment, Nino pose les mains sur la table. Le bois est lisse, un peu collant aussi. Le pot de confiture est rouge. L'étiquette montre une fraise. Je veux de la confiture, maman. Prends le pot, tout doucement. Nino prend le pot. Le verre est froid et lisse. Il tourne un peu le couvercle. Le couvercle ne vient pas. C'est trop difficile. Il est collé. Nino pose le pot. Il va vers maman. Aller vers eux, c'est possible. Il dit le besoin. Maman. J'ai besoin du pot. Le couvercle est trop dur. Je t'écoute, Nino. Viens. On le tient ensemble. Maman tient le pot. Nino tient le couvercle. Le couvercle fait un petit clic. Le pot s'ouvre. Ça sent la fraise. Bravo. Tu as dit le besoin. Tu es venu vers maman. C'est du bon travail. Merci, maman. Papa s'assoit près de lui. Tu tartines le pain ? Oui, papa. Nino tartine le pain. La confiture est rouge et brillante. Une petite graine de fraise reste sur le couteau. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Le rideau jaune bouge un tout petit peu. La mouche s'en va. Ça sent bon, hein ? Ça sent la fraise. Tu as fini de tartiner ? Presque, maman. Nino goûte un peu de confiture. Le pain est tiède sous ses doigts. Bravo, Nino. La cuillère en bois n'est plus seule.</t>
+          <t>La cuillère en bois dort dans une tache de confiture. La tache est rouge et un peu collante. Le rideau jaune ne bouge presque pas. Une mouche tapote la vitre, tout doucement. La cuisine sent le pain encore chaud. Des miettes dorées brillent sur la table. Maman essuie l'évier avec un linge bleu. Papa range les tasses dans le placard. Le pain est encore tiède, Nino. Tu veux un peu de confiture ? En ce moment, Nino pose les mains sur la table. Le bois est lisse, un peu collant aussi. Le pot de confiture est rouge. L'étiquette montre une fraise. Je veux de la confiture, maman. Prends le pot, tout doucement. Nino prend le pot. Le verre est froid et lisse. Il tourne un peu le couvercle. Le couvercle ne vient pas. C'est trop difficile. Il est collé. Nino pose le pot. Il va vers maman. Aller vers eux, c'est possible. Il dit le besoin. Maman. J'ai besoin du pot. Le couvercle est trop dur. Je t'écoute, Nino. Viens. On le tient ensemble. Maman tient le pot. Nino tient le couvercle. Le couvercle fait un petit clic. Le pot s'ouvre. Ça sent la fraise. Bravo. Tu as dit le besoin. Tu es venu vers maman. Merci, maman. Papa s'assoit près de lui. Tu tartines le pain ? Oui, papa. Nino tartine le pain. La confiture est rouge et brillante. Une petite graine de fraise reste sur le couteau. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Le rideau jaune bouge un tout petit peu. La mouche s'en va. Ça sent bon, hein ? Ça sent la fraise. Tu as fini de tartiner ? Presque, maman. Nino goûte un peu de confiture. Le pain est tiède sous ses doigts. Bravo, Nino. La cuillère en bois n'est plus seule.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules est dans la cuisine. Il veut de la confiture. Le pot est fermé. Jules tourne un peu. C'est trop difficile. Jules va vers la porte. Il va vers maman. Maman est près de l'évier. Jules dit : maman. J'ai besoin du pot. Il dit le besoin. Maman écoute. Maman ouvre le pot. Papa arrive. Jules dit merci. On peut &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Jules tartine le pain. Ça sent la fraise. Papa s'assoit près de lui.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La cuillère en bois dort dans une tache de confiture. La tache est rouge et un peu collante. Le rideau jaune ne bouge presque pas. Une mouche tapote la vitre, tout doucement. La cuisine sent le pain encore chaud. Des miettes dorées brillent sur la table. Maman essuie l'évier avec un linge bleu. Papa range les tasses dans le placard. Le pain est encore tiède, Nino. Tu veux un peu de confiture ? En ce moment, Nino pose les mains sur la table. Le bois est lisse, un peu collant aussi. Le pot de confiture est rouge. L'étiquette montre une fraise. Je veux de la confiture, maman. Prends le pot, tout doucement. Nino prend le pot. Le verre est froid et lisse. Il tourne un peu le couvercle. Le couvercle ne vient pas. C'est trop difficile. Il est collé. Nino pose le pot. Il va vers maman. Aller vers eux, c'est possible. Il dit le besoin. Maman. J'ai besoin du pot. Le couvercle est trop dur. Je t'écoute, Nino. Viens. On le tient ensemble. Maman tient le pot. Nino tient le couvercle. Le couvercle fait un petit clic. Le pot s'ouvre. Ça sent la fraise. Bravo. Tu as dit le besoin. Tu es venu vers maman. Merci, maman. Papa s'assoit près de lui. Tu tartines le pain ? Oui, papa. Nino tartine le pain. La confiture est rouge et brillante. Une petite graine de fraise reste sur le couteau. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Parce qu'il a dit le besoin, le pot s'ouvre. Le rideau jaune bouge un tout petit peu. La mouche s'en va. Ça sent bon, hein ? Ça sent la fraise. Tu as fini de tartiner ? Presque, maman. Nino goûte un peu de confiture. Le pain est tiède sous ses doigts. Bravo, Nino. La cuillère en bois n'est plus seule.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,7 +1361,6 @@
 narrateur|Ça sent la fraise.
 maman|Bravo. Tu as dit le besoin.
 papa|Tu es venu vers maman.
-papa|C'est du bon travail.
 enfant-m|Merci, maman.
 narrateur|Papa s'assoit près de lui.
 papa|Tu tartines le pain ?
@@ -1419,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules n'arrive pas. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1598,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a appelé. Il est allé vers maman. Il a dit le besoin. Maman a entendu. Le pot est ouvert. Tu es venu me le dire. Bravo. C'est du bon travail, Nino. Tu as fini ta tartine ? Oui, papa. Une miette reste sur la table. Elle brille un peu, comme la confiture.</t>
+          <t>Nino a appelé. Il est allé vers maman. Il a dit le besoin. Maman a entendu. Le pot est ouvert. Tu es venu me le dire. Bravo. Tu as fini ta tartine ? Oui, papa. Une miette reste sur la table. Elle brille un peu, comme la confiture.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules a appelé. Il a dit le besoin. Maman a entendu. Le pot est ouvert.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a appelé. Il est allé vers maman. Il a dit le besoin. Maman a entendu. Le pot est ouvert. Tu es venu me le dire. Bravo. Tu as fini ta tartine ? Oui, papa. Une miette reste sur la table. Elle brille un peu, comme la confiture.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,7 +1744,6 @@
 narrateur|Le pot est ouvert.
 maman|Tu es venu me le dire.
 maman|Bravo.
-papa|C'est du bon travail, Nino.
 papa|Tu as fini ta tartine ?
 enfant-m|Oui, papa.
 narrateur|Une miette reste sur la table.
@@ -1781,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules croque le pain. Papa s'assoit près de lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino croque le pain. Ça croustille tout doucement. C'est bon ? C'est bon, papa. Tu veux un verre d'eau ? Oui, maman. Maman pose un verre. L'eau fait un petit bruit clair. Papa s'assoit près de lui. On reste encore un peu ensemble ? Oui. La cuisine est calme. Le rideau jaune est immobile.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1951,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Nino. Tu as fait du bon travail. La tache de confiture a disparu. L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Nino. La tache de confiture a disparu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Nino. La tache de confiture a disparu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,9 +2092,7 @@
           <t>enfant-m|J'ai dit le besoin.
 maman|Oui. Tu es venu vers moi.
 papa|Bravo, Nino.
-papa|Tu as fait du bon travail.
-narrateur|La tache de confiture a disparu.
-narrateur|L'histoire est finie.</t>
+narrateur|La tache de confiture a disparu.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2158,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, maman, papa</t>
+          <t>Nino, maman, papa</t>
         </is>
       </c>
     </row>
